--- a/Histograma-CEP/Histograma-CEP-modelo.xlsx
+++ b/Histograma-CEP/Histograma-CEP-modelo.xlsx
@@ -130,7 +130,7 @@
     <t xml:space="preserve">Sinais</t>
   </si>
   <si>
-    <t xml:space="preserve">Na ordem: média fora dos limites; amplitude fora do limite; sete médias seguidas do mesmo lado da linha central; seis médias seguidas subindo ou descendo.</t>
+    <t xml:space="preserve">Na média, vale a primeira regra, nesta ordem: média fora dos limites; sete médias seguidas do mesmo lado da linha central; seis médias seguidas subindo ou descendo. A amplitude fora do limite é marcada junto, separada por ponto e vírgula.</t>
   </si>
   <si>
     <t xml:space="preserve">Capacidade</t>
@@ -772,7 +772,7 @@
     <t xml:space="preserve">Sim</t>
   </si>
   <si>
-    <t xml:space="preserve">Resistência da zona 3 queimada; bobina segregada e moída (RNC 2027-29).</t>
+    <t xml:space="preserve">Resistência da zona 3 queimada; bobina segregada e moída (registro de produto não conforme 2027-29).</t>
   </si>
 </sst>
 </file>
@@ -1982,11 +1982,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="9569555"/>
-        <c:axId val="8562166"/>
+        <c:axId val="72369229"/>
+        <c:axId val="45614552"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="9569555"/>
+        <c:axId val="72369229"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2018,7 +2018,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8562166"/>
+        <c:crossAx val="45614552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2026,7 +2026,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8562166"/>
+        <c:axId val="45614552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2099,7 +2099,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9569555"/>
+        <c:crossAx val="72369229"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2662,11 +2662,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="31112036"/>
-        <c:axId val="27400931"/>
+        <c:axId val="91714055"/>
+        <c:axId val="76436748"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="31112036"/>
+        <c:axId val="91714055"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2698,7 +2698,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27400931"/>
+        <c:crossAx val="76436748"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2706,7 +2706,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27400931"/>
+        <c:axId val="76436748"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2779,7 +2779,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31112036"/>
+        <c:crossAx val="91714055"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2948,11 +2948,11 @@
         </c:ser>
         <c:gapWidth val="10"/>
         <c:overlap val="0"/>
-        <c:axId val="58090363"/>
-        <c:axId val="26572483"/>
+        <c:axId val="57064887"/>
+        <c:axId val="51379062"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58090363"/>
+        <c:axId val="57064887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2984,7 +2984,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26572483"/>
+        <c:crossAx val="51379062"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2992,7 +2992,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26572483"/>
+        <c:axId val="51379062"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -3032,7 +3032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58090363"/>
+        <c:crossAx val="57064887"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3974,11 +3974,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="35318504"/>
-        <c:axId val="2227862"/>
+        <c:axId val="59008491"/>
+        <c:axId val="97360331"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="35318504"/>
+        <c:axId val="59008491"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4010,7 +4010,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2227862"/>
+        <c:crossAx val="97360331"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4018,7 +4018,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2227862"/>
+        <c:axId val="97360331"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4091,7 +4091,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35318504"/>
+        <c:crossAx val="59008491"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4834,11 +4834,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="45310917"/>
-        <c:axId val="58414738"/>
+        <c:axId val="26634049"/>
+        <c:axId val="54435706"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="45310917"/>
+        <c:axId val="26634049"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4870,7 +4870,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58414738"/>
+        <c:crossAx val="54435706"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4878,7 +4878,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58414738"/>
+        <c:axId val="54435706"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4951,7 +4951,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45310917"/>
+        <c:crossAx val="26634049"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5917,11 +5917,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="97069895"/>
-        <c:axId val="27371778"/>
+        <c:axId val="51381740"/>
+        <c:axId val="56916815"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97069895"/>
+        <c:axId val="51381740"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5953,7 +5953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27371778"/>
+        <c:crossAx val="56916815"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5961,7 +5961,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27371778"/>
+        <c:axId val="56916815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6034,7 +6034,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97069895"/>
+        <c:crossAx val="51381740"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6777,11 +6777,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="4080447"/>
-        <c:axId val="66446570"/>
+        <c:axId val="81948397"/>
+        <c:axId val="33900478"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="4080447"/>
+        <c:axId val="81948397"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6813,7 +6813,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66446570"/>
+        <c:crossAx val="33900478"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6821,7 +6821,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66446570"/>
+        <c:axId val="33900478"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6894,7 +6894,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4080447"/>
+        <c:crossAx val="81948397"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7446,7 +7446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
         <v>18</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v/>
       </c>
       <c r="P13" s="22" t="str">
-        <f aca="false">IF(OR(L13="",$L$5=""),"",IF(OR(L13&gt;$L$6,L13&lt;$L$7),"Média fora dos limites",IF(M13&gt;$L$9,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L13="",$L$5=""),"",IF(OR(L13&gt;$L$6,L13&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M13&gt;$L$9,IF(IF(OR(L13&gt;$L$6,L13&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q13" s="22" t="str">
@@ -7984,7 +7984,7 @@
         <v/>
       </c>
       <c r="P14" s="22" t="str">
-        <f aca="false">IF(OR(L14="",$L$5=""),"",IF(OR(L14&gt;$L$6,L14&lt;$L$7),"Média fora dos limites",IF(M14&gt;$L$9,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L14="",$L$5=""),"",IF(OR(L14&gt;$L$6,L14&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M14&gt;$L$9,IF(IF(OR(L14&gt;$L$6,L14&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q14" s="22" t="str">
@@ -8022,7 +8022,7 @@
         <v/>
       </c>
       <c r="P15" s="22" t="str">
-        <f aca="false">IF(OR(L15="",$L$5=""),"",IF(OR(L15&gt;$L$6,L15&lt;$L$7),"Média fora dos limites",IF(M15&gt;$L$9,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L15="",$L$5=""),"",IF(OR(L15&gt;$L$6,L15&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M15&gt;$L$9,IF(IF(OR(L15&gt;$L$6,L15&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q15" s="22" t="str">
@@ -8060,7 +8060,7 @@
         <v/>
       </c>
       <c r="P16" s="22" t="str">
-        <f aca="false">IF(OR(L16="",$L$5=""),"",IF(OR(L16&gt;$L$6,L16&lt;$L$7),"Média fora dos limites",IF(M16&gt;$L$9,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L16="",$L$5=""),"",IF(OR(L16&gt;$L$6,L16&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M16&gt;$L$9,IF(IF(OR(L16&gt;$L$6,L16&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q16" s="22" t="str">
@@ -8098,7 +8098,7 @@
         <v/>
       </c>
       <c r="P17" s="22" t="str">
-        <f aca="false">IF(OR(L17="",$L$5=""),"",IF(OR(L17&gt;$L$6,L17&lt;$L$7),"Média fora dos limites",IF(M17&gt;$L$9,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L17="",$L$5=""),"",IF(OR(L17&gt;$L$6,L17&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M17&gt;$L$9,IF(IF(OR(L17&gt;$L$6,L17&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q17" s="22" t="str">
@@ -8136,7 +8136,7 @@
         <v/>
       </c>
       <c r="P18" s="22" t="str">
-        <f aca="false">IF(OR(L18="",$L$5=""),"",IF(OR(L18&gt;$L$6,L18&lt;$L$7),"Média fora dos limites",IF(M18&gt;$L$9,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(AND(COUNT(L13:L18)=6,OR(AND(L18&gt;L17,L17&gt;L16,L16&gt;L15,L15&gt;L14,L14&gt;L13),AND(L18&lt;L17,L17&lt;L16,L16&lt;L15,L15&lt;L14,L14&lt;L13))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L18="",$L$5=""),"",IF(OR(L18&gt;$L$6,L18&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(AND(COUNT(L13:L18)=6,OR(AND(L18&gt;L17,L17&gt;L16,L16&gt;L15,L15&gt;L14,L14&gt;L13),AND(L18&lt;L17,L17&lt;L16,L16&lt;L15,L15&lt;L14,L14&lt;L13))),"6 subindo ou descendo","")))&amp;IF(M18&gt;$L$9,IF(IF(OR(L18&gt;$L$6,L18&lt;$L$7),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(AND(COUNT(L13:L18)=6,OR(AND(L18&gt;L17,L17&gt;L16,L16&gt;L15,L15&gt;L14,L14&gt;L13),AND(L18&lt;L17,L17&lt;L16,L16&lt;L15,L15&lt;L14,L14&lt;L13))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q18" s="22" t="str">
@@ -8174,7 +8174,7 @@
         <v/>
       </c>
       <c r="P19" s="22" t="str">
-        <f aca="false">IF(OR(L19="",$L$5=""),"",IF(OR(L19&gt;$L$6,L19&lt;$L$7),"Média fora dos limites",IF(M19&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L13:L19,"&gt;"&amp;$L$5)=7,COUNTIF(L13:L19,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L14:L19)=6,OR(AND(L19&gt;L18,L18&gt;L17,L17&gt;L16,L16&gt;L15,L15&gt;L14),AND(L19&lt;L18,L18&lt;L17,L17&lt;L16,L16&lt;L15,L15&lt;L14))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L19="",$L$5=""),"",IF(OR(L19&gt;$L$6,L19&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L13:L19,"&gt;"&amp;$L$5)=7,COUNTIF(L13:L19,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L14:L19)=6,OR(AND(L19&gt;L18,L18&gt;L17,L17&gt;L16,L16&gt;L15,L15&gt;L14),AND(L19&lt;L18,L18&lt;L17,L17&lt;L16,L16&lt;L15,L15&lt;L14))),"6 subindo ou descendo","")))&amp;IF(M19&gt;$L$9,IF(IF(OR(L19&gt;$L$6,L19&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L13:L19,"&gt;"&amp;$L$5)=7,COUNTIF(L13:L19,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L14:L19)=6,OR(AND(L19&gt;L18,L18&gt;L17,L17&gt;L16,L16&gt;L15,L15&gt;L14),AND(L19&lt;L18,L18&lt;L17,L17&lt;L16,L16&lt;L15,L15&lt;L14))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q19" s="22" t="str">
@@ -8212,7 +8212,7 @@
         <v/>
       </c>
       <c r="P20" s="22" t="str">
-        <f aca="false">IF(OR(L20="",$L$5=""),"",IF(OR(L20&gt;$L$6,L20&lt;$L$7),"Média fora dos limites",IF(M20&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L14:L20,"&gt;"&amp;$L$5)=7,COUNTIF(L14:L20,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L15:L20)=6,OR(AND(L20&gt;L19,L19&gt;L18,L18&gt;L17,L17&gt;L16,L16&gt;L15),AND(L20&lt;L19,L19&lt;L18,L18&lt;L17,L17&lt;L16,L16&lt;L15))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L20="",$L$5=""),"",IF(OR(L20&gt;$L$6,L20&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L14:L20,"&gt;"&amp;$L$5)=7,COUNTIF(L14:L20,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L15:L20)=6,OR(AND(L20&gt;L19,L19&gt;L18,L18&gt;L17,L17&gt;L16,L16&gt;L15),AND(L20&lt;L19,L19&lt;L18,L18&lt;L17,L17&lt;L16,L16&lt;L15))),"6 subindo ou descendo","")))&amp;IF(M20&gt;$L$9,IF(IF(OR(L20&gt;$L$6,L20&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L14:L20,"&gt;"&amp;$L$5)=7,COUNTIF(L14:L20,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L15:L20)=6,OR(AND(L20&gt;L19,L19&gt;L18,L18&gt;L17,L17&gt;L16,L16&gt;L15),AND(L20&lt;L19,L19&lt;L18,L18&lt;L17,L17&lt;L16,L16&lt;L15))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q20" s="22" t="str">
@@ -8250,7 +8250,7 @@
         <v/>
       </c>
       <c r="P21" s="22" t="str">
-        <f aca="false">IF(OR(L21="",$L$5=""),"",IF(OR(L21&gt;$L$6,L21&lt;$L$7),"Média fora dos limites",IF(M21&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L15:L21,"&gt;"&amp;$L$5)=7,COUNTIF(L15:L21,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L16:L21)=6,OR(AND(L21&gt;L20,L20&gt;L19,L19&gt;L18,L18&gt;L17,L17&gt;L16),AND(L21&lt;L20,L20&lt;L19,L19&lt;L18,L18&lt;L17,L17&lt;L16))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L21="",$L$5=""),"",IF(OR(L21&gt;$L$6,L21&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L15:L21,"&gt;"&amp;$L$5)=7,COUNTIF(L15:L21,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L16:L21)=6,OR(AND(L21&gt;L20,L20&gt;L19,L19&gt;L18,L18&gt;L17,L17&gt;L16),AND(L21&lt;L20,L20&lt;L19,L19&lt;L18,L18&lt;L17,L17&lt;L16))),"6 subindo ou descendo","")))&amp;IF(M21&gt;$L$9,IF(IF(OR(L21&gt;$L$6,L21&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L15:L21,"&gt;"&amp;$L$5)=7,COUNTIF(L15:L21,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L16:L21)=6,OR(AND(L21&gt;L20,L20&gt;L19,L19&gt;L18,L18&gt;L17,L17&gt;L16),AND(L21&lt;L20,L20&lt;L19,L19&lt;L18,L18&lt;L17,L17&lt;L16))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q21" s="22" t="str">
@@ -8288,7 +8288,7 @@
         <v/>
       </c>
       <c r="P22" s="22" t="str">
-        <f aca="false">IF(OR(L22="",$L$5=""),"",IF(OR(L22&gt;$L$6,L22&lt;$L$7),"Média fora dos limites",IF(M22&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L16:L22,"&gt;"&amp;$L$5)=7,COUNTIF(L16:L22,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L17:L22)=6,OR(AND(L22&gt;L21,L21&gt;L20,L20&gt;L19,L19&gt;L18,L18&gt;L17),AND(L22&lt;L21,L21&lt;L20,L20&lt;L19,L19&lt;L18,L18&lt;L17))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L22="",$L$5=""),"",IF(OR(L22&gt;$L$6,L22&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L16:L22,"&gt;"&amp;$L$5)=7,COUNTIF(L16:L22,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L17:L22)=6,OR(AND(L22&gt;L21,L21&gt;L20,L20&gt;L19,L19&gt;L18,L18&gt;L17),AND(L22&lt;L21,L21&lt;L20,L20&lt;L19,L19&lt;L18,L18&lt;L17))),"6 subindo ou descendo","")))&amp;IF(M22&gt;$L$9,IF(IF(OR(L22&gt;$L$6,L22&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L16:L22,"&gt;"&amp;$L$5)=7,COUNTIF(L16:L22,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L17:L22)=6,OR(AND(L22&gt;L21,L21&gt;L20,L20&gt;L19,L19&gt;L18,L18&gt;L17),AND(L22&lt;L21,L21&lt;L20,L20&lt;L19,L19&lt;L18,L18&lt;L17))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q22" s="22" t="str">
@@ -8326,7 +8326,7 @@
         <v/>
       </c>
       <c r="P23" s="22" t="str">
-        <f aca="false">IF(OR(L23="",$L$5=""),"",IF(OR(L23&gt;$L$6,L23&lt;$L$7),"Média fora dos limites",IF(M23&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L17:L23,"&gt;"&amp;$L$5)=7,COUNTIF(L17:L23,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L18:L23)=6,OR(AND(L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19,L19&gt;L18),AND(L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19,L19&lt;L18))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L23="",$L$5=""),"",IF(OR(L23&gt;$L$6,L23&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L17:L23,"&gt;"&amp;$L$5)=7,COUNTIF(L17:L23,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L18:L23)=6,OR(AND(L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19,L19&gt;L18),AND(L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19,L19&lt;L18))),"6 subindo ou descendo","")))&amp;IF(M23&gt;$L$9,IF(IF(OR(L23&gt;$L$6,L23&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L17:L23,"&gt;"&amp;$L$5)=7,COUNTIF(L17:L23,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L18:L23)=6,OR(AND(L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19,L19&gt;L18),AND(L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19,L19&lt;L18))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q23" s="22" t="str">
@@ -8364,7 +8364,7 @@
         <v/>
       </c>
       <c r="P24" s="22" t="str">
-        <f aca="false">IF(OR(L24="",$L$5=""),"",IF(OR(L24&gt;$L$6,L24&lt;$L$7),"Média fora dos limites",IF(M24&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L18:L24,"&gt;"&amp;$L$5)=7,COUNTIF(L18:L24,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L19:L24)=6,OR(AND(L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19),AND(L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L24="",$L$5=""),"",IF(OR(L24&gt;$L$6,L24&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L18:L24,"&gt;"&amp;$L$5)=7,COUNTIF(L18:L24,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L19:L24)=6,OR(AND(L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19),AND(L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19))),"6 subindo ou descendo","")))&amp;IF(M24&gt;$L$9,IF(IF(OR(L24&gt;$L$6,L24&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L18:L24,"&gt;"&amp;$L$5)=7,COUNTIF(L18:L24,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L19:L24)=6,OR(AND(L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19),AND(L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q24" s="22" t="str">
@@ -8402,7 +8402,7 @@
         <v/>
       </c>
       <c r="P25" s="22" t="str">
-        <f aca="false">IF(OR(L25="",$L$5=""),"",IF(OR(L25&gt;$L$6,L25&lt;$L$7),"Média fora dos limites",IF(M25&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L19:L25,"&gt;"&amp;$L$5)=7,COUNTIF(L19:L25,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L20:L25)=6,OR(AND(L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20),AND(L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L25="",$L$5=""),"",IF(OR(L25&gt;$L$6,L25&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L19:L25,"&gt;"&amp;$L$5)=7,COUNTIF(L19:L25,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L20:L25)=6,OR(AND(L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20),AND(L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20))),"6 subindo ou descendo","")))&amp;IF(M25&gt;$L$9,IF(IF(OR(L25&gt;$L$6,L25&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L19:L25,"&gt;"&amp;$L$5)=7,COUNTIF(L19:L25,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L20:L25)=6,OR(AND(L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20),AND(L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q25" s="22" t="str">
@@ -8440,7 +8440,7 @@
         <v/>
       </c>
       <c r="P26" s="22" t="str">
-        <f aca="false">IF(OR(L26="",$L$5=""),"",IF(OR(L26&gt;$L$6,L26&lt;$L$7),"Média fora dos limites",IF(M26&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L20:L26,"&gt;"&amp;$L$5)=7,COUNTIF(L20:L26,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L21:L26)=6,OR(AND(L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21),AND(L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L26="",$L$5=""),"",IF(OR(L26&gt;$L$6,L26&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L20:L26,"&gt;"&amp;$L$5)=7,COUNTIF(L20:L26,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L21:L26)=6,OR(AND(L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21),AND(L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21))),"6 subindo ou descendo","")))&amp;IF(M26&gt;$L$9,IF(IF(OR(L26&gt;$L$6,L26&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L20:L26,"&gt;"&amp;$L$5)=7,COUNTIF(L20:L26,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L21:L26)=6,OR(AND(L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21),AND(L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q26" s="22" t="str">
@@ -8478,7 +8478,7 @@
         <v/>
       </c>
       <c r="P27" s="22" t="str">
-        <f aca="false">IF(OR(L27="",$L$5=""),"",IF(OR(L27&gt;$L$6,L27&lt;$L$7),"Média fora dos limites",IF(M27&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L21:L27,"&gt;"&amp;$L$5)=7,COUNTIF(L21:L27,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L22:L27)=6,OR(AND(L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22),AND(L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L27="",$L$5=""),"",IF(OR(L27&gt;$L$6,L27&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L21:L27,"&gt;"&amp;$L$5)=7,COUNTIF(L21:L27,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L22:L27)=6,OR(AND(L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22),AND(L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22))),"6 subindo ou descendo","")))&amp;IF(M27&gt;$L$9,IF(IF(OR(L27&gt;$L$6,L27&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L21:L27,"&gt;"&amp;$L$5)=7,COUNTIF(L21:L27,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L22:L27)=6,OR(AND(L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22),AND(L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q27" s="22" t="str">
@@ -8516,7 +8516,7 @@
         <v/>
       </c>
       <c r="P28" s="22" t="str">
-        <f aca="false">IF(OR(L28="",$L$5=""),"",IF(OR(L28&gt;$L$6,L28&lt;$L$7),"Média fora dos limites",IF(M28&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L22:L28,"&gt;"&amp;$L$5)=7,COUNTIF(L22:L28,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L23:L28)=6,OR(AND(L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23),AND(L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L28="",$L$5=""),"",IF(OR(L28&gt;$L$6,L28&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L22:L28,"&gt;"&amp;$L$5)=7,COUNTIF(L22:L28,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L23:L28)=6,OR(AND(L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23),AND(L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23))),"6 subindo ou descendo","")))&amp;IF(M28&gt;$L$9,IF(IF(OR(L28&gt;$L$6,L28&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L22:L28,"&gt;"&amp;$L$5)=7,COUNTIF(L22:L28,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L23:L28)=6,OR(AND(L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23),AND(L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q28" s="22" t="str">
@@ -8554,7 +8554,7 @@
         <v/>
       </c>
       <c r="P29" s="22" t="str">
-        <f aca="false">IF(OR(L29="",$L$5=""),"",IF(OR(L29&gt;$L$6,L29&lt;$L$7),"Média fora dos limites",IF(M29&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L23:L29,"&gt;"&amp;$L$5)=7,COUNTIF(L23:L29,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L24:L29)=6,OR(AND(L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24),AND(L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L29="",$L$5=""),"",IF(OR(L29&gt;$L$6,L29&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L23:L29,"&gt;"&amp;$L$5)=7,COUNTIF(L23:L29,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L24:L29)=6,OR(AND(L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24),AND(L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24))),"6 subindo ou descendo","")))&amp;IF(M29&gt;$L$9,IF(IF(OR(L29&gt;$L$6,L29&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L23:L29,"&gt;"&amp;$L$5)=7,COUNTIF(L23:L29,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L24:L29)=6,OR(AND(L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24),AND(L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q29" s="22" t="str">
@@ -8592,7 +8592,7 @@
         <v/>
       </c>
       <c r="P30" s="22" t="str">
-        <f aca="false">IF(OR(L30="",$L$5=""),"",IF(OR(L30&gt;$L$6,L30&lt;$L$7),"Média fora dos limites",IF(M30&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L24:L30,"&gt;"&amp;$L$5)=7,COUNTIF(L24:L30,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L25:L30)=6,OR(AND(L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25),AND(L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L30="",$L$5=""),"",IF(OR(L30&gt;$L$6,L30&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L24:L30,"&gt;"&amp;$L$5)=7,COUNTIF(L24:L30,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L25:L30)=6,OR(AND(L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25),AND(L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25))),"6 subindo ou descendo","")))&amp;IF(M30&gt;$L$9,IF(IF(OR(L30&gt;$L$6,L30&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L24:L30,"&gt;"&amp;$L$5)=7,COUNTIF(L24:L30,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L25:L30)=6,OR(AND(L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25),AND(L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q30" s="22" t="str">
@@ -8630,7 +8630,7 @@
         <v/>
       </c>
       <c r="P31" s="22" t="str">
-        <f aca="false">IF(OR(L31="",$L$5=""),"",IF(OR(L31&gt;$L$6,L31&lt;$L$7),"Média fora dos limites",IF(M31&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L25:L31,"&gt;"&amp;$L$5)=7,COUNTIF(L25:L31,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L26:L31)=6,OR(AND(L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26),AND(L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L31="",$L$5=""),"",IF(OR(L31&gt;$L$6,L31&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L25:L31,"&gt;"&amp;$L$5)=7,COUNTIF(L25:L31,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L26:L31)=6,OR(AND(L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26),AND(L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26))),"6 subindo ou descendo","")))&amp;IF(M31&gt;$L$9,IF(IF(OR(L31&gt;$L$6,L31&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L25:L31,"&gt;"&amp;$L$5)=7,COUNTIF(L25:L31,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L26:L31)=6,OR(AND(L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26),AND(L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q31" s="22" t="str">
@@ -8668,7 +8668,7 @@
         <v/>
       </c>
       <c r="P32" s="22" t="str">
-        <f aca="false">IF(OR(L32="",$L$5=""),"",IF(OR(L32&gt;$L$6,L32&lt;$L$7),"Média fora dos limites",IF(M32&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L26:L32,"&gt;"&amp;$L$5)=7,COUNTIF(L26:L32,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L27:L32)=6,OR(AND(L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27),AND(L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L32="",$L$5=""),"",IF(OR(L32&gt;$L$6,L32&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L26:L32,"&gt;"&amp;$L$5)=7,COUNTIF(L26:L32,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L27:L32)=6,OR(AND(L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27),AND(L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27))),"6 subindo ou descendo","")))&amp;IF(M32&gt;$L$9,IF(IF(OR(L32&gt;$L$6,L32&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L26:L32,"&gt;"&amp;$L$5)=7,COUNTIF(L26:L32,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L27:L32)=6,OR(AND(L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27),AND(L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q32" s="22" t="str">
@@ -8706,7 +8706,7 @@
         <v/>
       </c>
       <c r="P33" s="22" t="str">
-        <f aca="false">IF(OR(L33="",$L$5=""),"",IF(OR(L33&gt;$L$6,L33&lt;$L$7),"Média fora dos limites",IF(M33&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L27:L33,"&gt;"&amp;$L$5)=7,COUNTIF(L27:L33,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L28:L33)=6,OR(AND(L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28),AND(L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L33="",$L$5=""),"",IF(OR(L33&gt;$L$6,L33&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L27:L33,"&gt;"&amp;$L$5)=7,COUNTIF(L27:L33,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L28:L33)=6,OR(AND(L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28),AND(L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28))),"6 subindo ou descendo","")))&amp;IF(M33&gt;$L$9,IF(IF(OR(L33&gt;$L$6,L33&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L27:L33,"&gt;"&amp;$L$5)=7,COUNTIF(L27:L33,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L28:L33)=6,OR(AND(L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28),AND(L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q33" s="22" t="str">
@@ -8744,7 +8744,7 @@
         <v/>
       </c>
       <c r="P34" s="22" t="str">
-        <f aca="false">IF(OR(L34="",$L$5=""),"",IF(OR(L34&gt;$L$6,L34&lt;$L$7),"Média fora dos limites",IF(M34&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L28:L34,"&gt;"&amp;$L$5)=7,COUNTIF(L28:L34,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L29:L34)=6,OR(AND(L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29),AND(L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L34="",$L$5=""),"",IF(OR(L34&gt;$L$6,L34&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L28:L34,"&gt;"&amp;$L$5)=7,COUNTIF(L28:L34,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L29:L34)=6,OR(AND(L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29),AND(L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29))),"6 subindo ou descendo","")))&amp;IF(M34&gt;$L$9,IF(IF(OR(L34&gt;$L$6,L34&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L28:L34,"&gt;"&amp;$L$5)=7,COUNTIF(L28:L34,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L29:L34)=6,OR(AND(L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29),AND(L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q34" s="22" t="str">
@@ -8782,7 +8782,7 @@
         <v/>
       </c>
       <c r="P35" s="22" t="str">
-        <f aca="false">IF(OR(L35="",$L$5=""),"",IF(OR(L35&gt;$L$6,L35&lt;$L$7),"Média fora dos limites",IF(M35&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L29:L35,"&gt;"&amp;$L$5)=7,COUNTIF(L29:L35,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L30:L35)=6,OR(AND(L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30),AND(L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L35="",$L$5=""),"",IF(OR(L35&gt;$L$6,L35&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L29:L35,"&gt;"&amp;$L$5)=7,COUNTIF(L29:L35,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L30:L35)=6,OR(AND(L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30),AND(L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30))),"6 subindo ou descendo","")))&amp;IF(M35&gt;$L$9,IF(IF(OR(L35&gt;$L$6,L35&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L29:L35,"&gt;"&amp;$L$5)=7,COUNTIF(L29:L35,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L30:L35)=6,OR(AND(L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30),AND(L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q35" s="22" t="str">
@@ -8820,7 +8820,7 @@
         <v/>
       </c>
       <c r="P36" s="22" t="str">
-        <f aca="false">IF(OR(L36="",$L$5=""),"",IF(OR(L36&gt;$L$6,L36&lt;$L$7),"Média fora dos limites",IF(M36&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L30:L36,"&gt;"&amp;$L$5)=7,COUNTIF(L30:L36,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L31:L36)=6,OR(AND(L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31),AND(L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L36="",$L$5=""),"",IF(OR(L36&gt;$L$6,L36&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L30:L36,"&gt;"&amp;$L$5)=7,COUNTIF(L30:L36,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L31:L36)=6,OR(AND(L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31),AND(L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31))),"6 subindo ou descendo","")))&amp;IF(M36&gt;$L$9,IF(IF(OR(L36&gt;$L$6,L36&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L30:L36,"&gt;"&amp;$L$5)=7,COUNTIF(L30:L36,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L31:L36)=6,OR(AND(L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31),AND(L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q36" s="22" t="str">
@@ -8858,7 +8858,7 @@
         <v/>
       </c>
       <c r="P37" s="22" t="str">
-        <f aca="false">IF(OR(L37="",$L$5=""),"",IF(OR(L37&gt;$L$6,L37&lt;$L$7),"Média fora dos limites",IF(M37&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L31:L37,"&gt;"&amp;$L$5)=7,COUNTIF(L31:L37,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L32:L37)=6,OR(AND(L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32),AND(L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L37="",$L$5=""),"",IF(OR(L37&gt;$L$6,L37&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L31:L37,"&gt;"&amp;$L$5)=7,COUNTIF(L31:L37,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L32:L37)=6,OR(AND(L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32),AND(L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32))),"6 subindo ou descendo","")))&amp;IF(M37&gt;$L$9,IF(IF(OR(L37&gt;$L$6,L37&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L31:L37,"&gt;"&amp;$L$5)=7,COUNTIF(L31:L37,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L32:L37)=6,OR(AND(L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32),AND(L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q37" s="22" t="str">
@@ -8896,7 +8896,7 @@
         <v/>
       </c>
       <c r="P38" s="22" t="str">
-        <f aca="false">IF(OR(L38="",$L$5=""),"",IF(OR(L38&gt;$L$6,L38&lt;$L$7),"Média fora dos limites",IF(M38&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L32:L38,"&gt;"&amp;$L$5)=7,COUNTIF(L32:L38,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L33:L38)=6,OR(AND(L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33),AND(L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L38="",$L$5=""),"",IF(OR(L38&gt;$L$6,L38&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L32:L38,"&gt;"&amp;$L$5)=7,COUNTIF(L32:L38,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L33:L38)=6,OR(AND(L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33),AND(L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33))),"6 subindo ou descendo","")))&amp;IF(M38&gt;$L$9,IF(IF(OR(L38&gt;$L$6,L38&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L32:L38,"&gt;"&amp;$L$5)=7,COUNTIF(L32:L38,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L33:L38)=6,OR(AND(L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33),AND(L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q38" s="22" t="str">
@@ -8934,7 +8934,7 @@
         <v/>
       </c>
       <c r="P39" s="22" t="str">
-        <f aca="false">IF(OR(L39="",$L$5=""),"",IF(OR(L39&gt;$L$6,L39&lt;$L$7),"Média fora dos limites",IF(M39&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L33:L39,"&gt;"&amp;$L$5)=7,COUNTIF(L33:L39,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L34:L39)=6,OR(AND(L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34),AND(L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L39="",$L$5=""),"",IF(OR(L39&gt;$L$6,L39&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L33:L39,"&gt;"&amp;$L$5)=7,COUNTIF(L33:L39,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L34:L39)=6,OR(AND(L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34),AND(L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34))),"6 subindo ou descendo","")))&amp;IF(M39&gt;$L$9,IF(IF(OR(L39&gt;$L$6,L39&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L33:L39,"&gt;"&amp;$L$5)=7,COUNTIF(L33:L39,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L34:L39)=6,OR(AND(L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34),AND(L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q39" s="22" t="str">
@@ -8972,7 +8972,7 @@
         <v/>
       </c>
       <c r="P40" s="22" t="str">
-        <f aca="false">IF(OR(L40="",$L$5=""),"",IF(OR(L40&gt;$L$6,L40&lt;$L$7),"Média fora dos limites",IF(M40&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L34:L40,"&gt;"&amp;$L$5)=7,COUNTIF(L34:L40,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L35:L40)=6,OR(AND(L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35),AND(L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L40="",$L$5=""),"",IF(OR(L40&gt;$L$6,L40&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L34:L40,"&gt;"&amp;$L$5)=7,COUNTIF(L34:L40,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L35:L40)=6,OR(AND(L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35),AND(L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35))),"6 subindo ou descendo","")))&amp;IF(M40&gt;$L$9,IF(IF(OR(L40&gt;$L$6,L40&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L34:L40,"&gt;"&amp;$L$5)=7,COUNTIF(L34:L40,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L35:L40)=6,OR(AND(L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35),AND(L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q40" s="22" t="str">
@@ -9010,7 +9010,7 @@
         <v/>
       </c>
       <c r="P41" s="22" t="str">
-        <f aca="false">IF(OR(L41="",$L$5=""),"",IF(OR(L41&gt;$L$6,L41&lt;$L$7),"Média fora dos limites",IF(M41&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L35:L41,"&gt;"&amp;$L$5)=7,COUNTIF(L35:L41,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L36:L41)=6,OR(AND(L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36),AND(L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L41="",$L$5=""),"",IF(OR(L41&gt;$L$6,L41&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L35:L41,"&gt;"&amp;$L$5)=7,COUNTIF(L35:L41,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L36:L41)=6,OR(AND(L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36),AND(L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36))),"6 subindo ou descendo","")))&amp;IF(M41&gt;$L$9,IF(IF(OR(L41&gt;$L$6,L41&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L35:L41,"&gt;"&amp;$L$5)=7,COUNTIF(L35:L41,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L36:L41)=6,OR(AND(L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36),AND(L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q41" s="22" t="str">
@@ -9048,7 +9048,7 @@
         <v/>
       </c>
       <c r="P42" s="22" t="str">
-        <f aca="false">IF(OR(L42="",$L$5=""),"",IF(OR(L42&gt;$L$6,L42&lt;$L$7),"Média fora dos limites",IF(M42&gt;$L$9,"Amplitude fora do limite",IF(OR(COUNTIF(L36:L42,"&gt;"&amp;$L$5)=7,COUNTIF(L36:L42,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L37:L42)=6,OR(AND(L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37),AND(L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L42="",$L$5=""),"",IF(OR(L42&gt;$L$6,L42&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L36:L42,"&gt;"&amp;$L$5)=7,COUNTIF(L36:L42,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L37:L42)=6,OR(AND(L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37),AND(L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37))),"6 subindo ou descendo","")))&amp;IF(M42&gt;$L$9,IF(IF(OR(L42&gt;$L$6,L42&lt;$L$7),"Média fora dos limites",IF(OR(COUNTIF(L36:L42,"&gt;"&amp;$L$5)=7,COUNTIF(L36:L42,"&lt;"&amp;$L$5)=7),"7 do mesmo lado",IF(AND(COUNT(L37:L42)=6,OR(AND(L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37),AND(L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q42" s="22" t="str">
@@ -9106,7 +9106,7 @@
       <c r="C46" s="24"/>
       <c r="D46" s="24"/>
       <c r="E46" s="25" t="str">
-        <f aca="false">COUNTIF(P13:P42,"Média fora dos limites")&amp;" média fora dos limites"&amp;", "&amp;COUNTIF(P13:P42,"Amplitude fora do limite")&amp;" amplitude fora do limite"&amp;", "&amp;COUNTIF(P13:P42,"7 do mesmo lado")&amp;" 7 do mesmo lado"&amp;", "&amp;COUNTIF(P13:P42,"6 subindo ou descendo")&amp;" 6 subindo ou descendo"</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("Média fora dos limites",P13:P42)))&amp;" média fora dos limites"&amp;", "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("Amplitude fora do limite",P13:P42)))&amp;" amplitude fora do limite"&amp;", "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("7 do mesmo lado",P13:P42)))&amp;" 7 do mesmo lado"&amp;", "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("6 subindo ou descendo",P13:P42)))&amp;" 6 subindo ou descendo"</f>
         <v>0 média fora dos limites, 0 amplitude fora do limite, 0 7 do mesmo lado, 0 6 subindo ou descendo</v>
       </c>
       <c r="F46" s="25"/>
@@ -9171,16 +9171,16 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:P42">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>P13="Média fora dos limites"</formula>
+      <formula>ISNUMBER(SEARCH("Média fora dos limites",P13))</formula>
     </cfRule>
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>P13="Amplitude fora do limite"</formula>
+      <formula>ISNUMBER(SEARCH("Amplitude fora do limite",P13))</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>P13="7 do mesmo lado"</formula>
+      <formula>ISNUMBER(SEARCH("7 do mesmo lado",P13))</formula>
     </cfRule>
     <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>P13="6 subindo ou descendo"</formula>
+      <formula>ISNUMBER(SEARCH("6 subindo ou descendo",P13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q13:Q42">
@@ -10867,7 +10867,7 @@
         <v>136</v>
       </c>
       <c r="C13" s="8" t="n">
-        <f aca="false">COUNTIF(Dados!$P$13:$P$42,"Média fora dos limites")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("Média fora dos limites",Dados!$P$13:$P$42)))</f>
         <v>0</v>
       </c>
       <c r="D13" s="30" t="s">
@@ -10881,7 +10881,7 @@
         <v>138</v>
       </c>
       <c r="C14" s="8" t="n">
-        <f aca="false">COUNTIF(Dados!$P$13:$P$42,"Amplitude fora do limite")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("Amplitude fora do limite",Dados!$P$13:$P$42)))</f>
         <v>0</v>
       </c>
       <c r="D14" s="30" t="s">
@@ -10895,7 +10895,7 @@
         <v>140</v>
       </c>
       <c r="C15" s="8" t="n">
-        <f aca="false">COUNTIF(Dados!$P$13:$P$42,"7 do mesmo lado")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("7 do mesmo lado",Dados!$P$13:$P$42)))</f>
         <v>0</v>
       </c>
       <c r="D15" s="30" t="s">
@@ -10909,7 +10909,7 @@
         <v>142</v>
       </c>
       <c r="C16" s="8" t="n">
-        <f aca="false">COUNTIF(Dados!$P$13:$P$42,"6 subindo ou descendo")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("6 subindo ou descendo",Dados!$P$13:$P$42)))</f>
         <v>0</v>
       </c>
       <c r="D16" s="30" t="s">
@@ -11863,7 +11863,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="22" t="str">
-        <f aca="false">IF(OR(L19="",$L$11=""),"",IF(OR(L19&gt;$L$12,L19&lt;$L$13),"Média fora dos limites",IF(M19&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L19="",$L$11=""),"",IF(OR(L19&gt;$L$12,L19&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M19&gt;$L$15,IF(IF(OR(L19&gt;$L$12,L19&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q19" s="22" t="str">
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="22" t="str">
-        <f aca="false">IF(OR(L20="",$L$11=""),"",IF(OR(L20&gt;$L$12,L20&lt;$L$13),"Média fora dos limites",IF(M20&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L20="",$L$11=""),"",IF(OR(L20&gt;$L$12,L20&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M20&gt;$L$15,IF(IF(OR(L20&gt;$L$12,L20&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q20" s="22" t="str">
@@ -12007,7 +12007,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="22" t="str">
-        <f aca="false">IF(OR(L21="",$L$11=""),"",IF(OR(L21&gt;$L$12,L21&lt;$L$13),"Média fora dos limites",IF(M21&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L21="",$L$11=""),"",IF(OR(L21&gt;$L$12,L21&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M21&gt;$L$15,IF(IF(OR(L21&gt;$L$12,L21&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q21" s="22" t="str">
@@ -12079,7 +12079,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="22" t="str">
-        <f aca="false">IF(OR(L22="",$L$11=""),"",IF(OR(L22&gt;$L$12,L22&lt;$L$13),"Média fora dos limites",IF(M22&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L22="",$L$11=""),"",IF(OR(L22&gt;$L$12,L22&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M22&gt;$L$15,IF(IF(OR(L22&gt;$L$12,L22&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q22" s="22" t="str">
@@ -12151,7 +12151,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="22" t="str">
-        <f aca="false">IF(OR(L23="",$L$11=""),"",IF(OR(L23&gt;$L$12,L23&lt;$L$13),"Média fora dos limites",IF(M23&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L23="",$L$11=""),"",IF(OR(L23&gt;$L$12,L23&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M23&gt;$L$15,IF(IF(OR(L23&gt;$L$12,L23&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q23" s="22" t="str">
@@ -12223,7 +12223,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="22" t="str">
-        <f aca="false">IF(OR(L24="",$L$11=""),"",IF(OR(L24&gt;$L$12,L24&lt;$L$13),"Média fora dos limites",IF(M24&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(AND(COUNT(L19:L24)=6,OR(AND(L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19),AND(L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L24="",$L$11=""),"",IF(OR(L24&gt;$L$12,L24&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(AND(COUNT(L19:L24)=6,OR(AND(L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19),AND(L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19))),"6 subindo ou descendo","")))&amp;IF(M24&gt;$L$15,IF(IF(OR(L24&gt;$L$12,L24&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(AND(COUNT(L19:L24)=6,OR(AND(L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19),AND(L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q24" s="22" t="str">
@@ -12295,7 +12295,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="22" t="str">
-        <f aca="false">IF(OR(L25="",$L$11=""),"",IF(OR(L25&gt;$L$12,L25&lt;$L$13),"Média fora dos limites",IF(M25&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L19:L25,"&gt;"&amp;$L$11)=7,COUNTIF(L19:L25,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L20:L25)=6,OR(AND(L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20),AND(L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L25="",$L$11=""),"",IF(OR(L25&gt;$L$12,L25&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L19:L25,"&gt;"&amp;$L$11)=7,COUNTIF(L19:L25,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L20:L25)=6,OR(AND(L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20),AND(L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20))),"6 subindo ou descendo","")))&amp;IF(M25&gt;$L$15,IF(IF(OR(L25&gt;$L$12,L25&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L19:L25,"&gt;"&amp;$L$11)=7,COUNTIF(L19:L25,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L20:L25)=6,OR(AND(L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20),AND(L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q25" s="22" t="str">
@@ -12367,7 +12367,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="22" t="str">
-        <f aca="false">IF(OR(L26="",$L$11=""),"",IF(OR(L26&gt;$L$12,L26&lt;$L$13),"Média fora dos limites",IF(M26&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L20:L26,"&gt;"&amp;$L$11)=7,COUNTIF(L20:L26,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L21:L26)=6,OR(AND(L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21),AND(L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L26="",$L$11=""),"",IF(OR(L26&gt;$L$12,L26&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L20:L26,"&gt;"&amp;$L$11)=7,COUNTIF(L20:L26,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L21:L26)=6,OR(AND(L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21),AND(L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21))),"6 subindo ou descendo","")))&amp;IF(M26&gt;$L$15,IF(IF(OR(L26&gt;$L$12,L26&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L20:L26,"&gt;"&amp;$L$11)=7,COUNTIF(L20:L26,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L21:L26)=6,OR(AND(L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21),AND(L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q26" s="22" t="str">
@@ -12439,7 +12439,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="22" t="str">
-        <f aca="false">IF(OR(L27="",$L$11=""),"",IF(OR(L27&gt;$L$12,L27&lt;$L$13),"Média fora dos limites",IF(M27&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L21:L27,"&gt;"&amp;$L$11)=7,COUNTIF(L21:L27,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L22:L27)=6,OR(AND(L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22),AND(L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L27="",$L$11=""),"",IF(OR(L27&gt;$L$12,L27&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L21:L27,"&gt;"&amp;$L$11)=7,COUNTIF(L21:L27,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L22:L27)=6,OR(AND(L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22),AND(L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22))),"6 subindo ou descendo","")))&amp;IF(M27&gt;$L$15,IF(IF(OR(L27&gt;$L$12,L27&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L21:L27,"&gt;"&amp;$L$11)=7,COUNTIF(L21:L27,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L22:L27)=6,OR(AND(L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22),AND(L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q27" s="22" t="str">
@@ -12511,7 +12511,7 @@
         <v>1</v>
       </c>
       <c r="P28" s="22" t="str">
-        <f aca="false">IF(OR(L28="",$L$11=""),"",IF(OR(L28&gt;$L$12,L28&lt;$L$13),"Média fora dos limites",IF(M28&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L22:L28,"&gt;"&amp;$L$11)=7,COUNTIF(L22:L28,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L23:L28)=6,OR(AND(L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23),AND(L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L28="",$L$11=""),"",IF(OR(L28&gt;$L$12,L28&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L22:L28,"&gt;"&amp;$L$11)=7,COUNTIF(L22:L28,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L23:L28)=6,OR(AND(L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23),AND(L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23))),"6 subindo ou descendo","")))&amp;IF(M28&gt;$L$15,IF(IF(OR(L28&gt;$L$12,L28&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L22:L28,"&gt;"&amp;$L$11)=7,COUNTIF(L22:L28,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L23:L28)=6,OR(AND(L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23),AND(L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q28" s="22" t="str">
@@ -12583,7 +12583,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="22" t="str">
-        <f aca="false">IF(OR(L29="",$L$11=""),"",IF(OR(L29&gt;$L$12,L29&lt;$L$13),"Média fora dos limites",IF(M29&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L23:L29,"&gt;"&amp;$L$11)=7,COUNTIF(L23:L29,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L24:L29)=6,OR(AND(L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24),AND(L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L29="",$L$11=""),"",IF(OR(L29&gt;$L$12,L29&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L23:L29,"&gt;"&amp;$L$11)=7,COUNTIF(L23:L29,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L24:L29)=6,OR(AND(L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24),AND(L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24))),"6 subindo ou descendo","")))&amp;IF(M29&gt;$L$15,IF(IF(OR(L29&gt;$L$12,L29&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L23:L29,"&gt;"&amp;$L$11)=7,COUNTIF(L23:L29,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L24:L29)=6,OR(AND(L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24),AND(L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q29" s="22" t="str">
@@ -12655,7 +12655,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="22" t="str">
-        <f aca="false">IF(OR(L30="",$L$11=""),"",IF(OR(L30&gt;$L$12,L30&lt;$L$13),"Média fora dos limites",IF(M30&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L24:L30,"&gt;"&amp;$L$11)=7,COUNTIF(L24:L30,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L25:L30)=6,OR(AND(L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25),AND(L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L30="",$L$11=""),"",IF(OR(L30&gt;$L$12,L30&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L24:L30,"&gt;"&amp;$L$11)=7,COUNTIF(L24:L30,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L25:L30)=6,OR(AND(L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25),AND(L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25))),"6 subindo ou descendo","")))&amp;IF(M30&gt;$L$15,IF(IF(OR(L30&gt;$L$12,L30&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L24:L30,"&gt;"&amp;$L$11)=7,COUNTIF(L24:L30,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L25:L30)=6,OR(AND(L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25),AND(L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q30" s="22" t="str">
@@ -12727,7 +12727,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="22" t="str">
-        <f aca="false">IF(OR(L31="",$L$11=""),"",IF(OR(L31&gt;$L$12,L31&lt;$L$13),"Média fora dos limites",IF(M31&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L25:L31,"&gt;"&amp;$L$11)=7,COUNTIF(L25:L31,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L26:L31)=6,OR(AND(L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26),AND(L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L31="",$L$11=""),"",IF(OR(L31&gt;$L$12,L31&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L25:L31,"&gt;"&amp;$L$11)=7,COUNTIF(L25:L31,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L26:L31)=6,OR(AND(L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26),AND(L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26))),"6 subindo ou descendo","")))&amp;IF(M31&gt;$L$15,IF(IF(OR(L31&gt;$L$12,L31&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L25:L31,"&gt;"&amp;$L$11)=7,COUNTIF(L25:L31,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L26:L31)=6,OR(AND(L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26),AND(L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q31" s="22" t="str">
@@ -12799,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="P32" s="22" t="str">
-        <f aca="false">IF(OR(L32="",$L$11=""),"",IF(OR(L32&gt;$L$12,L32&lt;$L$13),"Média fora dos limites",IF(M32&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L26:L32,"&gt;"&amp;$L$11)=7,COUNTIF(L26:L32,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L27:L32)=6,OR(AND(L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27),AND(L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L32="",$L$11=""),"",IF(OR(L32&gt;$L$12,L32&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L26:L32,"&gt;"&amp;$L$11)=7,COUNTIF(L26:L32,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L27:L32)=6,OR(AND(L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27),AND(L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27))),"6 subindo ou descendo","")))&amp;IF(M32&gt;$L$15,IF(IF(OR(L32&gt;$L$12,L32&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L26:L32,"&gt;"&amp;$L$11)=7,COUNTIF(L26:L32,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L27:L32)=6,OR(AND(L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27),AND(L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q32" s="22" t="str">
@@ -12871,7 +12871,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="22" t="str">
-        <f aca="false">IF(OR(L33="",$L$11=""),"",IF(OR(L33&gt;$L$12,L33&lt;$L$13),"Média fora dos limites",IF(M33&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L27:L33,"&gt;"&amp;$L$11)=7,COUNTIF(L27:L33,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L28:L33)=6,OR(AND(L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28),AND(L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L33="",$L$11=""),"",IF(OR(L33&gt;$L$12,L33&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L27:L33,"&gt;"&amp;$L$11)=7,COUNTIF(L27:L33,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L28:L33)=6,OR(AND(L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28),AND(L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28))),"6 subindo ou descendo","")))&amp;IF(M33&gt;$L$15,IF(IF(OR(L33&gt;$L$12,L33&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L27:L33,"&gt;"&amp;$L$11)=7,COUNTIF(L27:L33,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L28:L33)=6,OR(AND(L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28),AND(L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q33" s="22" t="str">
@@ -12943,7 +12943,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="22" t="str">
-        <f aca="false">IF(OR(L34="",$L$11=""),"",IF(OR(L34&gt;$L$12,L34&lt;$L$13),"Média fora dos limites",IF(M34&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L28:L34,"&gt;"&amp;$L$11)=7,COUNTIF(L28:L34,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L29:L34)=6,OR(AND(L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29),AND(L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L34="",$L$11=""),"",IF(OR(L34&gt;$L$12,L34&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L28:L34,"&gt;"&amp;$L$11)=7,COUNTIF(L28:L34,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L29:L34)=6,OR(AND(L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29),AND(L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29))),"6 subindo ou descendo","")))&amp;IF(M34&gt;$L$15,IF(IF(OR(L34&gt;$L$12,L34&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L28:L34,"&gt;"&amp;$L$11)=7,COUNTIF(L28:L34,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L29:L34)=6,OR(AND(L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29),AND(L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q34" s="22" t="str">
@@ -13015,7 +13015,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="22" t="str">
-        <f aca="false">IF(OR(L35="",$L$11=""),"",IF(OR(L35&gt;$L$12,L35&lt;$L$13),"Média fora dos limites",IF(M35&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L29:L35,"&gt;"&amp;$L$11)=7,COUNTIF(L29:L35,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L30:L35)=6,OR(AND(L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30),AND(L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L35="",$L$11=""),"",IF(OR(L35&gt;$L$12,L35&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L29:L35,"&gt;"&amp;$L$11)=7,COUNTIF(L29:L35,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L30:L35)=6,OR(AND(L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30),AND(L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30))),"6 subindo ou descendo","")))&amp;IF(M35&gt;$L$15,IF(IF(OR(L35&gt;$L$12,L35&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L29:L35,"&gt;"&amp;$L$11)=7,COUNTIF(L29:L35,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L30:L35)=6,OR(AND(L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30),AND(L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q35" s="22" t="str">
@@ -13087,7 +13087,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="22" t="str">
-        <f aca="false">IF(OR(L36="",$L$11=""),"",IF(OR(L36&gt;$L$12,L36&lt;$L$13),"Média fora dos limites",IF(M36&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L30:L36,"&gt;"&amp;$L$11)=7,COUNTIF(L30:L36,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L31:L36)=6,OR(AND(L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31),AND(L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L36="",$L$11=""),"",IF(OR(L36&gt;$L$12,L36&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L30:L36,"&gt;"&amp;$L$11)=7,COUNTIF(L30:L36,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L31:L36)=6,OR(AND(L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31),AND(L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31))),"6 subindo ou descendo","")))&amp;IF(M36&gt;$L$15,IF(IF(OR(L36&gt;$L$12,L36&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L30:L36,"&gt;"&amp;$L$11)=7,COUNTIF(L30:L36,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L31:L36)=6,OR(AND(L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31),AND(L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q36" s="22" t="str">
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="P37" s="22" t="str">
-        <f aca="false">IF(OR(L37="",$L$11=""),"",IF(OR(L37&gt;$L$12,L37&lt;$L$13),"Média fora dos limites",IF(M37&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L31:L37,"&gt;"&amp;$L$11)=7,COUNTIF(L31:L37,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L32:L37)=6,OR(AND(L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32),AND(L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L37="",$L$11=""),"",IF(OR(L37&gt;$L$12,L37&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L31:L37,"&gt;"&amp;$L$11)=7,COUNTIF(L31:L37,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L32:L37)=6,OR(AND(L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32),AND(L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32))),"6 subindo ou descendo","")))&amp;IF(M37&gt;$L$15,IF(IF(OR(L37&gt;$L$12,L37&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L31:L37,"&gt;"&amp;$L$11)=7,COUNTIF(L31:L37,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L32:L37)=6,OR(AND(L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32),AND(L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q37" s="22" t="str">
@@ -13231,7 +13231,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="22" t="str">
-        <f aca="false">IF(OR(L38="",$L$11=""),"",IF(OR(L38&gt;$L$12,L38&lt;$L$13),"Média fora dos limites",IF(M38&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L32:L38,"&gt;"&amp;$L$11)=7,COUNTIF(L32:L38,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L33:L38)=6,OR(AND(L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33),AND(L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L38="",$L$11=""),"",IF(OR(L38&gt;$L$12,L38&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L32:L38,"&gt;"&amp;$L$11)=7,COUNTIF(L32:L38,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L33:L38)=6,OR(AND(L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33),AND(L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33))),"6 subindo ou descendo","")))&amp;IF(M38&gt;$L$15,IF(IF(OR(L38&gt;$L$12,L38&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L32:L38,"&gt;"&amp;$L$11)=7,COUNTIF(L32:L38,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L33:L38)=6,OR(AND(L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33),AND(L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q38" s="22" t="str">
@@ -13303,7 +13303,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="22" t="str">
-        <f aca="false">IF(OR(L39="",$L$11=""),"",IF(OR(L39&gt;$L$12,L39&lt;$L$13),"Média fora dos limites",IF(M39&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L33:L39,"&gt;"&amp;$L$11)=7,COUNTIF(L33:L39,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L34:L39)=6,OR(AND(L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34),AND(L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L39="",$L$11=""),"",IF(OR(L39&gt;$L$12,L39&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L33:L39,"&gt;"&amp;$L$11)=7,COUNTIF(L33:L39,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L34:L39)=6,OR(AND(L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34),AND(L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34))),"6 subindo ou descendo","")))&amp;IF(M39&gt;$L$15,IF(IF(OR(L39&gt;$L$12,L39&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L33:L39,"&gt;"&amp;$L$11)=7,COUNTIF(L33:L39,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L34:L39)=6,OR(AND(L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34),AND(L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q39" s="22" t="str">
@@ -13375,7 +13375,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="22" t="str">
-        <f aca="false">IF(OR(L40="",$L$11=""),"",IF(OR(L40&gt;$L$12,L40&lt;$L$13),"Média fora dos limites",IF(M40&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L34:L40,"&gt;"&amp;$L$11)=7,COUNTIF(L34:L40,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L35:L40)=6,OR(AND(L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35),AND(L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L40="",$L$11=""),"",IF(OR(L40&gt;$L$12,L40&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L34:L40,"&gt;"&amp;$L$11)=7,COUNTIF(L34:L40,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L35:L40)=6,OR(AND(L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35),AND(L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35))),"6 subindo ou descendo","")))&amp;IF(M40&gt;$L$15,IF(IF(OR(L40&gt;$L$12,L40&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L34:L40,"&gt;"&amp;$L$11)=7,COUNTIF(L34:L40,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L35:L40)=6,OR(AND(L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35),AND(L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q40" s="22" t="str">
@@ -13447,7 +13447,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="22" t="str">
-        <f aca="false">IF(OR(L41="",$L$11=""),"",IF(OR(L41&gt;$L$12,L41&lt;$L$13),"Média fora dos limites",IF(M41&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L35:L41,"&gt;"&amp;$L$11)=7,COUNTIF(L35:L41,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L36:L41)=6,OR(AND(L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36),AND(L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L41="",$L$11=""),"",IF(OR(L41&gt;$L$12,L41&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L35:L41,"&gt;"&amp;$L$11)=7,COUNTIF(L35:L41,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L36:L41)=6,OR(AND(L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36),AND(L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36))),"6 subindo ou descendo","")))&amp;IF(M41&gt;$L$15,IF(IF(OR(L41&gt;$L$12,L41&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L35:L41,"&gt;"&amp;$L$11)=7,COUNTIF(L35:L41,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L36:L41)=6,OR(AND(L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36),AND(L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q41" s="22" t="str">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="22" t="str">
-        <f aca="false">IF(OR(L42="",$L$11=""),"",IF(OR(L42&gt;$L$12,L42&lt;$L$13),"Média fora dos limites",IF(M42&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L36:L42,"&gt;"&amp;$L$11)=7,COUNTIF(L36:L42,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L37:L42)=6,OR(AND(L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37),AND(L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L42="",$L$11=""),"",IF(OR(L42&gt;$L$12,L42&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L36:L42,"&gt;"&amp;$L$11)=7,COUNTIF(L36:L42,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L37:L42)=6,OR(AND(L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37),AND(L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37))),"6 subindo ou descendo","")))&amp;IF(M42&gt;$L$15,IF(IF(OR(L42&gt;$L$12,L42&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L36:L42,"&gt;"&amp;$L$11)=7,COUNTIF(L36:L42,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L37:L42)=6,OR(AND(L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37),AND(L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q42" s="22" t="str">
@@ -13591,7 +13591,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="22" t="str">
-        <f aca="false">IF(OR(L43="",$L$11=""),"",IF(OR(L43&gt;$L$12,L43&lt;$L$13),"Média fora dos limites",IF(M43&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L37:L43,"&gt;"&amp;$L$11)=7,COUNTIF(L37:L43,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L38:L43)=6,OR(AND(L43&gt;L42,L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38),AND(L43&lt;L42,L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L43="",$L$11=""),"",IF(OR(L43&gt;$L$12,L43&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L37:L43,"&gt;"&amp;$L$11)=7,COUNTIF(L37:L43,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L38:L43)=6,OR(AND(L43&gt;L42,L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38),AND(L43&lt;L42,L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38))),"6 subindo ou descendo","")))&amp;IF(M43&gt;$L$15,IF(IF(OR(L43&gt;$L$12,L43&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L37:L43,"&gt;"&amp;$L$11)=7,COUNTIF(L37:L43,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L38:L43)=6,OR(AND(L43&gt;L42,L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38),AND(L43&lt;L42,L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q43" s="22" t="str">
@@ -13855,7 +13855,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="8" t="n">
-        <f aca="false">COUNTIF($P$19:$P$43,"Média fora dos limites")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("Média fora dos limites",$P$19:$P$43)))</f>
         <v>0</v>
       </c>
       <c r="F70" s="8"/>
@@ -13880,7 +13880,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="8" t="n">
-        <f aca="false">COUNTIF($P$19:$P$43,"Amplitude fora do limite")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("Amplitude fora do limite",$P$19:$P$43)))</f>
         <v>0</v>
       </c>
       <c r="F71" s="8"/>
@@ -13905,7 +13905,7 @@
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="8" t="n">
-        <f aca="false">COUNTIF($P$19:$P$43,"7 do mesmo lado")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("7 do mesmo lado",$P$19:$P$43)))</f>
         <v>0</v>
       </c>
       <c r="F72" s="8"/>
@@ -13930,7 +13930,7 @@
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="8" t="n">
-        <f aca="false">COUNTIF($P$19:$P$43,"6 subindo ou descendo")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("6 subindo ou descendo",$P$19:$P$43)))</f>
         <v>0</v>
       </c>
       <c r="F73" s="8"/>
@@ -14306,16 +14306,16 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="P19:P43">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>P19="Média fora dos limites"</formula>
+      <formula>ISNUMBER(SEARCH("Média fora dos limites",P19))</formula>
     </cfRule>
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>P19="Amplitude fora do limite"</formula>
+      <formula>ISNUMBER(SEARCH("Amplitude fora do limite",P19))</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>P19="7 do mesmo lado"</formula>
+      <formula>ISNUMBER(SEARCH("7 do mesmo lado",P19))</formula>
     </cfRule>
     <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>P19="6 subindo ou descendo"</formula>
+      <formula>ISNUMBER(SEARCH("6 subindo ou descendo",P19))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q19:Q43">
@@ -14835,7 +14835,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="22" t="str">
-        <f aca="false">IF(OR(L19="",$L$11=""),"",IF(OR(L19&gt;$L$12,L19&lt;$L$13),"Média fora dos limites",IF(M19&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L19="",$L$11=""),"",IF(OR(L19&gt;$L$12,L19&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M19&gt;$L$15,IF(IF(OR(L19&gt;$L$12,L19&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q19" s="22" t="str">
@@ -14907,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="22" t="str">
-        <f aca="false">IF(OR(L20="",$L$11=""),"",IF(OR(L20&gt;$L$12,L20&lt;$L$13),"Média fora dos limites",IF(M20&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L20="",$L$11=""),"",IF(OR(L20&gt;$L$12,L20&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M20&gt;$L$15,IF(IF(OR(L20&gt;$L$12,L20&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q20" s="22" t="str">
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="22" t="str">
-        <f aca="false">IF(OR(L21="",$L$11=""),"",IF(OR(L21&gt;$L$12,L21&lt;$L$13),"Média fora dos limites",IF(M21&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L21="",$L$11=""),"",IF(OR(L21&gt;$L$12,L21&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M21&gt;$L$15,IF(IF(OR(L21&gt;$L$12,L21&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q21" s="22" t="str">
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="22" t="str">
-        <f aca="false">IF(OR(L22="",$L$11=""),"",IF(OR(L22&gt;$L$12,L22&lt;$L$13),"Média fora dos limites",IF(M22&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L22="",$L$11=""),"",IF(OR(L22&gt;$L$12,L22&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M22&gt;$L$15,IF(IF(OR(L22&gt;$L$12,L22&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q22" s="22" t="str">
@@ -15123,7 +15123,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="22" t="str">
-        <f aca="false">IF(OR(L23="",$L$11=""),"",IF(OR(L23&gt;$L$12,L23&lt;$L$13),"Média fora dos limites",IF(M23&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L23="",$L$11=""),"",IF(OR(L23&gt;$L$12,L23&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))&amp;IF(M23&gt;$L$15,IF(IF(OR(L23&gt;$L$12,L23&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(FALSE(),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q23" s="22" t="str">
@@ -15199,8 +15199,8 @@
         <v>0</v>
       </c>
       <c r="P24" s="22" t="str">
-        <f aca="false">IF(OR(L24="",$L$11=""),"",IF(OR(L24&gt;$L$12,L24&lt;$L$13),"Média fora dos limites",IF(M24&gt;$L$15,"Amplitude fora do limite",IF(FALSE(),"7 do mesmo lado",IF(AND(COUNT(L19:L24)=6,OR(AND(L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19),AND(L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19))),"6 subindo ou descendo","")))))</f>
-        <v>Média fora dos limites</v>
+        <f aca="false">IF(OR(L24="",$L$11=""),"",IF(OR(L24&gt;$L$12,L24&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(AND(COUNT(L19:L24)=6,OR(AND(L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19),AND(L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19))),"6 subindo ou descendo","")))&amp;IF(M24&gt;$L$15,IF(IF(OR(L24&gt;$L$12,L24&lt;$L$13),"Média fora dos limites",IF(FALSE(),"7 do mesmo lado",IF(AND(COUNT(L19:L24)=6,OR(AND(L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20,L20&gt;L19),AND(L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20,L20&lt;L19))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
+        <v>Média fora dos limites; Amplitude fora do limite</v>
       </c>
       <c r="Q24" s="22" t="str">
         <f aca="false">IF(COUNT(E24:I24)+LEN(C24)+LEN(D24)+LEN(J24)=0,"",IF(AND(COUNT(E24:I24)&gt;0,COUNT(E24:I24)&lt;5),"Faltam medições",IF(AND(COUNT(E24:I24)&gt;0,C24=""),"Falta a data",IF(AND(J24="Sim",K24=""),"Falta o motivo",IF(COUNT(E24:I24)=0,"Faltam medições","OK")))))</f>
@@ -15271,7 +15271,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="22" t="str">
-        <f aca="false">IF(OR(L25="",$L$11=""),"",IF(OR(L25&gt;$L$12,L25&lt;$L$13),"Média fora dos limites",IF(M25&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L19:L25,"&gt;"&amp;$L$11)=7,COUNTIF(L19:L25,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L20:L25)=6,OR(AND(L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20),AND(L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L25="",$L$11=""),"",IF(OR(L25&gt;$L$12,L25&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L19:L25,"&gt;"&amp;$L$11)=7,COUNTIF(L19:L25,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L20:L25)=6,OR(AND(L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20),AND(L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20))),"6 subindo ou descendo","")))&amp;IF(M25&gt;$L$15,IF(IF(OR(L25&gt;$L$12,L25&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L19:L25,"&gt;"&amp;$L$11)=7,COUNTIF(L19:L25,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L20:L25)=6,OR(AND(L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21,L21&gt;L20),AND(L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21,L21&lt;L20))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q25" s="22" t="str">
@@ -15343,7 +15343,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="22" t="str">
-        <f aca="false">IF(OR(L26="",$L$11=""),"",IF(OR(L26&gt;$L$12,L26&lt;$L$13),"Média fora dos limites",IF(M26&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L20:L26,"&gt;"&amp;$L$11)=7,COUNTIF(L20:L26,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L21:L26)=6,OR(AND(L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21),AND(L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L26="",$L$11=""),"",IF(OR(L26&gt;$L$12,L26&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L20:L26,"&gt;"&amp;$L$11)=7,COUNTIF(L20:L26,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L21:L26)=6,OR(AND(L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21),AND(L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21))),"6 subindo ou descendo","")))&amp;IF(M26&gt;$L$15,IF(IF(OR(L26&gt;$L$12,L26&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L20:L26,"&gt;"&amp;$L$11)=7,COUNTIF(L20:L26,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L21:L26)=6,OR(AND(L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22,L22&gt;L21),AND(L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22,L22&lt;L21))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q26" s="22" t="str">
@@ -15415,7 +15415,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="22" t="str">
-        <f aca="false">IF(OR(L27="",$L$11=""),"",IF(OR(L27&gt;$L$12,L27&lt;$L$13),"Média fora dos limites",IF(M27&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L21:L27,"&gt;"&amp;$L$11)=7,COUNTIF(L21:L27,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L22:L27)=6,OR(AND(L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22),AND(L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L27="",$L$11=""),"",IF(OR(L27&gt;$L$12,L27&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L21:L27,"&gt;"&amp;$L$11)=7,COUNTIF(L21:L27,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L22:L27)=6,OR(AND(L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22),AND(L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22))),"6 subindo ou descendo","")))&amp;IF(M27&gt;$L$15,IF(IF(OR(L27&gt;$L$12,L27&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L21:L27,"&gt;"&amp;$L$11)=7,COUNTIF(L21:L27,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L22:L27)=6,OR(AND(L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23,L23&gt;L22),AND(L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23,L23&lt;L22))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q27" s="22" t="str">
@@ -15487,7 +15487,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="22" t="str">
-        <f aca="false">IF(OR(L28="",$L$11=""),"",IF(OR(L28&gt;$L$12,L28&lt;$L$13),"Média fora dos limites",IF(M28&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L22:L28,"&gt;"&amp;$L$11)=7,COUNTIF(L22:L28,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L23:L28)=6,OR(AND(L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23),AND(L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L28="",$L$11=""),"",IF(OR(L28&gt;$L$12,L28&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L22:L28,"&gt;"&amp;$L$11)=7,COUNTIF(L22:L28,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L23:L28)=6,OR(AND(L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23),AND(L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23))),"6 subindo ou descendo","")))&amp;IF(M28&gt;$L$15,IF(IF(OR(L28&gt;$L$12,L28&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L22:L28,"&gt;"&amp;$L$11)=7,COUNTIF(L22:L28,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L23:L28)=6,OR(AND(L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24,L24&gt;L23),AND(L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24,L24&lt;L23))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q28" s="22" t="str">
@@ -15559,7 +15559,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="22" t="str">
-        <f aca="false">IF(OR(L29="",$L$11=""),"",IF(OR(L29&gt;$L$12,L29&lt;$L$13),"Média fora dos limites",IF(M29&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L23:L29,"&gt;"&amp;$L$11)=7,COUNTIF(L23:L29,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L24:L29)=6,OR(AND(L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24),AND(L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L29="",$L$11=""),"",IF(OR(L29&gt;$L$12,L29&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L23:L29,"&gt;"&amp;$L$11)=7,COUNTIF(L23:L29,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L24:L29)=6,OR(AND(L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24),AND(L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24))),"6 subindo ou descendo","")))&amp;IF(M29&gt;$L$15,IF(IF(OR(L29&gt;$L$12,L29&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L23:L29,"&gt;"&amp;$L$11)=7,COUNTIF(L23:L29,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L24:L29)=6,OR(AND(L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25,L25&gt;L24),AND(L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25,L25&lt;L24))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q29" s="22" t="str">
@@ -15631,7 +15631,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="22" t="str">
-        <f aca="false">IF(OR(L30="",$L$11=""),"",IF(OR(L30&gt;$L$12,L30&lt;$L$13),"Média fora dos limites",IF(M30&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L24:L30,"&gt;"&amp;$L$11)=7,COUNTIF(L24:L30,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L25:L30)=6,OR(AND(L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25),AND(L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L30="",$L$11=""),"",IF(OR(L30&gt;$L$12,L30&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L24:L30,"&gt;"&amp;$L$11)=7,COUNTIF(L24:L30,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L25:L30)=6,OR(AND(L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25),AND(L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25))),"6 subindo ou descendo","")))&amp;IF(M30&gt;$L$15,IF(IF(OR(L30&gt;$L$12,L30&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L24:L30,"&gt;"&amp;$L$11)=7,COUNTIF(L24:L30,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L25:L30)=6,OR(AND(L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26,L26&gt;L25),AND(L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26,L26&lt;L25))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q30" s="22" t="str">
@@ -15703,7 +15703,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="22" t="str">
-        <f aca="false">IF(OR(L31="",$L$11=""),"",IF(OR(L31&gt;$L$12,L31&lt;$L$13),"Média fora dos limites",IF(M31&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L25:L31,"&gt;"&amp;$L$11)=7,COUNTIF(L25:L31,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L26:L31)=6,OR(AND(L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26),AND(L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L31="",$L$11=""),"",IF(OR(L31&gt;$L$12,L31&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L25:L31,"&gt;"&amp;$L$11)=7,COUNTIF(L25:L31,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L26:L31)=6,OR(AND(L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26),AND(L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26))),"6 subindo ou descendo","")))&amp;IF(M31&gt;$L$15,IF(IF(OR(L31&gt;$L$12,L31&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L25:L31,"&gt;"&amp;$L$11)=7,COUNTIF(L25:L31,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L26:L31)=6,OR(AND(L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27,L27&gt;L26),AND(L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27,L27&lt;L26))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q31" s="22" t="str">
@@ -15775,7 +15775,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="22" t="str">
-        <f aca="false">IF(OR(L32="",$L$11=""),"",IF(OR(L32&gt;$L$12,L32&lt;$L$13),"Média fora dos limites",IF(M32&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L26:L32,"&gt;"&amp;$L$11)=7,COUNTIF(L26:L32,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L27:L32)=6,OR(AND(L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27),AND(L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L32="",$L$11=""),"",IF(OR(L32&gt;$L$12,L32&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L26:L32,"&gt;"&amp;$L$11)=7,COUNTIF(L26:L32,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L27:L32)=6,OR(AND(L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27),AND(L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27))),"6 subindo ou descendo","")))&amp;IF(M32&gt;$L$15,IF(IF(OR(L32&gt;$L$12,L32&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L26:L32,"&gt;"&amp;$L$11)=7,COUNTIF(L26:L32,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L27:L32)=6,OR(AND(L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28,L28&gt;L27),AND(L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28,L28&lt;L27))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q32" s="22" t="str">
@@ -15847,7 +15847,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="22" t="str">
-        <f aca="false">IF(OR(L33="",$L$11=""),"",IF(OR(L33&gt;$L$12,L33&lt;$L$13),"Média fora dos limites",IF(M33&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L27:L33,"&gt;"&amp;$L$11)=7,COUNTIF(L27:L33,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L28:L33)=6,OR(AND(L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28),AND(L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L33="",$L$11=""),"",IF(OR(L33&gt;$L$12,L33&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L27:L33,"&gt;"&amp;$L$11)=7,COUNTIF(L27:L33,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L28:L33)=6,OR(AND(L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28),AND(L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28))),"6 subindo ou descendo","")))&amp;IF(M33&gt;$L$15,IF(IF(OR(L33&gt;$L$12,L33&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L27:L33,"&gt;"&amp;$L$11)=7,COUNTIF(L27:L33,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L28:L33)=6,OR(AND(L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29,L29&gt;L28),AND(L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29,L29&lt;L28))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q33" s="22" t="str">
@@ -15919,7 +15919,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="22" t="str">
-        <f aca="false">IF(OR(L34="",$L$11=""),"",IF(OR(L34&gt;$L$12,L34&lt;$L$13),"Média fora dos limites",IF(M34&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L28:L34,"&gt;"&amp;$L$11)=7,COUNTIF(L28:L34,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L29:L34)=6,OR(AND(L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29),AND(L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L34="",$L$11=""),"",IF(OR(L34&gt;$L$12,L34&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L28:L34,"&gt;"&amp;$L$11)=7,COUNTIF(L28:L34,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L29:L34)=6,OR(AND(L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29),AND(L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29))),"6 subindo ou descendo","")))&amp;IF(M34&gt;$L$15,IF(IF(OR(L34&gt;$L$12,L34&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L28:L34,"&gt;"&amp;$L$11)=7,COUNTIF(L28:L34,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L29:L34)=6,OR(AND(L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30,L30&gt;L29),AND(L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30,L30&lt;L29))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q34" s="22" t="str">
@@ -15991,7 +15991,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="22" t="str">
-        <f aca="false">IF(OR(L35="",$L$11=""),"",IF(OR(L35&gt;$L$12,L35&lt;$L$13),"Média fora dos limites",IF(M35&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L29:L35,"&gt;"&amp;$L$11)=7,COUNTIF(L29:L35,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L30:L35)=6,OR(AND(L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30),AND(L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L35="",$L$11=""),"",IF(OR(L35&gt;$L$12,L35&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L29:L35,"&gt;"&amp;$L$11)=7,COUNTIF(L29:L35,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L30:L35)=6,OR(AND(L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30),AND(L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30))),"6 subindo ou descendo","")))&amp;IF(M35&gt;$L$15,IF(IF(OR(L35&gt;$L$12,L35&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L29:L35,"&gt;"&amp;$L$11)=7,COUNTIF(L29:L35,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L30:L35)=6,OR(AND(L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31,L31&gt;L30),AND(L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31,L31&lt;L30))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q35" s="22" t="str">
@@ -16063,7 +16063,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="22" t="str">
-        <f aca="false">IF(OR(L36="",$L$11=""),"",IF(OR(L36&gt;$L$12,L36&lt;$L$13),"Média fora dos limites",IF(M36&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L30:L36,"&gt;"&amp;$L$11)=7,COUNTIF(L30:L36,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L31:L36)=6,OR(AND(L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31),AND(L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L36="",$L$11=""),"",IF(OR(L36&gt;$L$12,L36&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L30:L36,"&gt;"&amp;$L$11)=7,COUNTIF(L30:L36,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L31:L36)=6,OR(AND(L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31),AND(L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31))),"6 subindo ou descendo","")))&amp;IF(M36&gt;$L$15,IF(IF(OR(L36&gt;$L$12,L36&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L30:L36,"&gt;"&amp;$L$11)=7,COUNTIF(L30:L36,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L31:L36)=6,OR(AND(L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32,L32&gt;L31),AND(L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32,L32&lt;L31))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v/>
       </c>
       <c r="Q36" s="22" t="str">
@@ -16135,7 +16135,7 @@
         <v>0</v>
       </c>
       <c r="P37" s="22" t="str">
-        <f aca="false">IF(OR(L37="",$L$11=""),"",IF(OR(L37&gt;$L$12,L37&lt;$L$13),"Média fora dos limites",IF(M37&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L31:L37,"&gt;"&amp;$L$11)=7,COUNTIF(L31:L37,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L32:L37)=6,OR(AND(L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32),AND(L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L37="",$L$11=""),"",IF(OR(L37&gt;$L$12,L37&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L31:L37,"&gt;"&amp;$L$11)=7,COUNTIF(L31:L37,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L32:L37)=6,OR(AND(L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32),AND(L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32))),"6 subindo ou descendo","")))&amp;IF(M37&gt;$L$15,IF(IF(OR(L37&gt;$L$12,L37&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L31:L37,"&gt;"&amp;$L$11)=7,COUNTIF(L31:L37,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L32:L37)=6,OR(AND(L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33,L33&gt;L32),AND(L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33,L33&lt;L32))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v>Média fora dos limites</v>
       </c>
       <c r="Q37" s="22" t="str">
@@ -16207,8 +16207,8 @@
         <v>0</v>
       </c>
       <c r="P38" s="22" t="str">
-        <f aca="false">IF(OR(L38="",$L$11=""),"",IF(OR(L38&gt;$L$12,L38&lt;$L$13),"Média fora dos limites",IF(M38&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L32:L38,"&gt;"&amp;$L$11)=7,COUNTIF(L32:L38,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L33:L38)=6,OR(AND(L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33),AND(L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33))),"6 subindo ou descendo","")))))</f>
-        <v>Média fora dos limites</v>
+        <f aca="false">IF(OR(L38="",$L$11=""),"",IF(OR(L38&gt;$L$12,L38&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L32:L38,"&gt;"&amp;$L$11)=7,COUNTIF(L32:L38,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L33:L38)=6,OR(AND(L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33),AND(L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33))),"6 subindo ou descendo","")))&amp;IF(M38&gt;$L$15,IF(IF(OR(L38&gt;$L$12,L38&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L32:L38,"&gt;"&amp;$L$11)=7,COUNTIF(L32:L38,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L33:L38)=6,OR(AND(L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34,L34&gt;L33),AND(L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34,L34&lt;L33))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
+        <v>Média fora dos limites; Amplitude fora do limite</v>
       </c>
       <c r="Q38" s="22" t="str">
         <f aca="false">IF(COUNT(E38:I38)+LEN(C38)+LEN(D38)+LEN(J38)=0,"",IF(AND(COUNT(E38:I38)&gt;0,COUNT(E38:I38)&lt;5),"Faltam medições",IF(AND(COUNT(E38:I38)&gt;0,C38=""),"Falta a data",IF(AND(J38="Sim",K38=""),"Falta o motivo",IF(COUNT(E38:I38)=0,"Faltam medições","OK")))))</f>
@@ -16279,7 +16279,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="22" t="str">
-        <f aca="false">IF(OR(L39="",$L$11=""),"",IF(OR(L39&gt;$L$12,L39&lt;$L$13),"Média fora dos limites",IF(M39&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L33:L39,"&gt;"&amp;$L$11)=7,COUNTIF(L33:L39,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L34:L39)=6,OR(AND(L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34),AND(L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L39="",$L$11=""),"",IF(OR(L39&gt;$L$12,L39&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L33:L39,"&gt;"&amp;$L$11)=7,COUNTIF(L33:L39,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L34:L39)=6,OR(AND(L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34),AND(L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34))),"6 subindo ou descendo","")))&amp;IF(M39&gt;$L$15,IF(IF(OR(L39&gt;$L$12,L39&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L33:L39,"&gt;"&amp;$L$11)=7,COUNTIF(L33:L39,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L34:L39)=6,OR(AND(L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35,L35&gt;L34),AND(L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35,L35&lt;L34))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v>Média fora dos limites</v>
       </c>
       <c r="Q39" s="22" t="str">
@@ -16351,7 +16351,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="22" t="str">
-        <f aca="false">IF(OR(L40="",$L$11=""),"",IF(OR(L40&gt;$L$12,L40&lt;$L$13),"Média fora dos limites",IF(M40&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L34:L40,"&gt;"&amp;$L$11)=7,COUNTIF(L34:L40,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L35:L40)=6,OR(AND(L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35),AND(L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L40="",$L$11=""),"",IF(OR(L40&gt;$L$12,L40&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L34:L40,"&gt;"&amp;$L$11)=7,COUNTIF(L34:L40,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L35:L40)=6,OR(AND(L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35),AND(L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35))),"6 subindo ou descendo","")))&amp;IF(M40&gt;$L$15,IF(IF(OR(L40&gt;$L$12,L40&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L34:L40,"&gt;"&amp;$L$11)=7,COUNTIF(L34:L40,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L35:L40)=6,OR(AND(L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36,L36&gt;L35),AND(L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36,L36&lt;L35))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v>Média fora dos limites</v>
       </c>
       <c r="Q40" s="22" t="str">
@@ -16423,7 +16423,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="22" t="str">
-        <f aca="false">IF(OR(L41="",$L$11=""),"",IF(OR(L41&gt;$L$12,L41&lt;$L$13),"Média fora dos limites",IF(M41&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L35:L41,"&gt;"&amp;$L$11)=7,COUNTIF(L35:L41,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L36:L41)=6,OR(AND(L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36),AND(L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L41="",$L$11=""),"",IF(OR(L41&gt;$L$12,L41&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L35:L41,"&gt;"&amp;$L$11)=7,COUNTIF(L35:L41,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L36:L41)=6,OR(AND(L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36),AND(L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36))),"6 subindo ou descendo","")))&amp;IF(M41&gt;$L$15,IF(IF(OR(L41&gt;$L$12,L41&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L35:L41,"&gt;"&amp;$L$11)=7,COUNTIF(L35:L41,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L36:L41)=6,OR(AND(L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37,L37&gt;L36),AND(L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37,L37&lt;L36))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v>Média fora dos limites</v>
       </c>
       <c r="Q41" s="22" t="str">
@@ -16495,7 +16495,7 @@
         <v>2</v>
       </c>
       <c r="P42" s="22" t="str">
-        <f aca="false">IF(OR(L42="",$L$11=""),"",IF(OR(L42&gt;$L$12,L42&lt;$L$13),"Média fora dos limites",IF(M42&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L36:L42,"&gt;"&amp;$L$11)=7,COUNTIF(L36:L42,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L37:L42)=6,OR(AND(L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37),AND(L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L42="",$L$11=""),"",IF(OR(L42&gt;$L$12,L42&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L36:L42,"&gt;"&amp;$L$11)=7,COUNTIF(L36:L42,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L37:L42)=6,OR(AND(L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37),AND(L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37))),"6 subindo ou descendo","")))&amp;IF(M42&gt;$L$15,IF(IF(OR(L42&gt;$L$12,L42&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L36:L42,"&gt;"&amp;$L$11)=7,COUNTIF(L36:L42,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L37:L42)=6,OR(AND(L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38,L38&gt;L37),AND(L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38,L38&lt;L37))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v>Média fora dos limites</v>
       </c>
       <c r="Q42" s="22" t="str">
@@ -16567,7 +16567,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="22" t="str">
-        <f aca="false">IF(OR(L43="",$L$11=""),"",IF(OR(L43&gt;$L$12,L43&lt;$L$13),"Média fora dos limites",IF(M43&gt;$L$15,"Amplitude fora do limite",IF(OR(COUNTIF(L37:L43,"&gt;"&amp;$L$11)=7,COUNTIF(L37:L43,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L38:L43)=6,OR(AND(L43&gt;L42,L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38),AND(L43&lt;L42,L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38))),"6 subindo ou descendo","")))))</f>
+        <f aca="false">IF(OR(L43="",$L$11=""),"",IF(OR(L43&gt;$L$12,L43&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L37:L43,"&gt;"&amp;$L$11)=7,COUNTIF(L37:L43,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L38:L43)=6,OR(AND(L43&gt;L42,L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38),AND(L43&lt;L42,L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38))),"6 subindo ou descendo","")))&amp;IF(M43&gt;$L$15,IF(IF(OR(L43&gt;$L$12,L43&lt;$L$13),"Média fora dos limites",IF(OR(COUNTIF(L37:L43,"&gt;"&amp;$L$11)=7,COUNTIF(L37:L43,"&lt;"&amp;$L$11)=7),"7 do mesmo lado",IF(AND(COUNT(L38:L43)=6,OR(AND(L43&gt;L42,L42&gt;L41,L41&gt;L40,L40&gt;L39,L39&gt;L38),AND(L43&lt;L42,L42&lt;L41,L41&lt;L40,L40&lt;L39,L39&lt;L38))),"6 subindo ou descendo","")))="","","; ")&amp;"Amplitude fora do limite",""))</f>
         <v>Média fora dos limites</v>
       </c>
       <c r="Q43" s="22" t="str">
@@ -16831,7 +16831,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="8" t="n">
-        <f aca="false">COUNTIF($P$19:$P$43,"Média fora dos limites")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("Média fora dos limites",$P$19:$P$43)))</f>
         <v>8</v>
       </c>
       <c r="F70" s="8"/>
@@ -16856,8 +16856,8 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="8" t="n">
-        <f aca="false">COUNTIF($P$19:$P$43,"Amplitude fora do limite")</f>
-        <v>0</v>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("Amplitude fora do limite",$P$19:$P$43)))</f>
+        <v>2</v>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="30" t="s">
@@ -16881,7 +16881,7 @@
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="8" t="n">
-        <f aca="false">COUNTIF($P$19:$P$43,"7 do mesmo lado")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("7 do mesmo lado",$P$19:$P$43)))</f>
         <v>0</v>
       </c>
       <c r="F72" s="8"/>
@@ -16906,7 +16906,7 @@
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="8" t="n">
-        <f aca="false">COUNTIF($P$19:$P$43,"6 subindo ou descendo")</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("6 subindo ou descendo",$P$19:$P$43)))</f>
         <v>0</v>
       </c>
       <c r="F73" s="8"/>
@@ -17282,16 +17282,16 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="P19:P43">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>P19="Média fora dos limites"</formula>
+      <formula>ISNUMBER(SEARCH("Média fora dos limites",P19))</formula>
     </cfRule>
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>P19="Amplitude fora do limite"</formula>
+      <formula>ISNUMBER(SEARCH("Amplitude fora do limite",P19))</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>P19="7 do mesmo lado"</formula>
+      <formula>ISNUMBER(SEARCH("7 do mesmo lado",P19))</formula>
     </cfRule>
     <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>P19="6 subindo ou descendo"</formula>
+      <formula>ISNUMBER(SEARCH("6 subindo ou descendo",P19))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q19:Q43">
